--- a/vse-loti/339406910/spec-339406910.xlsx
+++ b/vse-loti/339406910/spec-339406910.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>трубы (от Т 74 до Т 75) Вытесненный объем грунта который не будет завозиться: 67,79+(0,936+0,845+1,769+2,3)=73,64 м3 -  песчаное основание+трубы и футляры Откопка камеры  Т74 =16,73 м3 Объём разбираемого асфальтобетонного покрытия= 19*1,15*0,13 = 2,84 м3 Объём щебеночного основания для восстановления дорог = 19*1,15*0,3 = 6,56 м3 Объём обратной засыпки 297-73,64-(2,84+6,56)=213,96 м3 1 Перевозка грузов I класса автомобилями-самосвалами грузоподъемностью 10 т работающих вне карьера на расстояние до 3 км 1 т груза 406,524 2 Засыпка траншей и котлованов с перемещением грунта до 5 м бульдозерами мощностью: 59 кВт (80 л.с.), группа грунтов 2 м3 214 3 Уплотнение грунта пневматическими трамбовками, группа грунтов: 1-2 м3 42,79 4 Устройство подстилающих и выравнивающих слоев оснований: из щебня м3 6,56 5 Планировка площадей бульдозерами мощностью: 59 кВт (80л.с.) м2 655 Разборка камеры Т74 6 Демонтаж чугунных люков шт 1 7 Демонтаж плит перекрытий камер площадью: до 5 м2 шт 2 8 Демонтаж блоков стен подвалов массой: до 0,5 т (фбс 9.4.6) шт 9 9 Демонтаж блоков стен подвалов массой: до 1,5 т (фбс 24.4.6) шт 9 10 Разборка кирпичной кладки камеры  вручную: без очистки кирпича м3 0,5 Демонтаж трубопровода  в камере Т74 11 Демонтаж стальных трубопроводов в ТК при номинальном давлении 1,6 МПа, температуре 150°С, диаметр труб: 65 мм + з/арматура км 0,003175 12 Демонтаж стальных трубопроводов в ТК при номинальном давлении 1,6 МПа, температуре 150°С, диаметр труб: 150 мм + з/арматура км 0,0109 ЧИСТКА КАМЕР согласно п.4 общих указаний чер.277/2026-ТС л.1.8 13 Очистка камер: от сухого ила и грязи без труб и арматуры м3 0,3 Транспортировка строительного мусора на полигон ТБО 14 Погрузо-разгрузочные работы при автомобильных перевозках: Погрузка мусора строительного с погрузкой экскаваторами емкостью ковша до 0,5 м3  изоляция, кирпич 1 т груза 1,05 15 Перевозка грузов I класса автомобилями-самосвалами грузоподъемностью 10 т работающих вне карьера на расстояние до 8 км 1 т груза 1,05 16 Погрузка при автомобильных перевозках изделий из сборного железобетона, бетона, керамзитобетона массой до 3 т 1 т груза 15,784 17 Перевозка грузов I класса автомобилями-самосвалами грузоподъемностью 10 т работающих вне карьера на расстояние до 8 км 1 т груза 15,784 18 Разгрузка при автомобильных перевозках изделий из сборного железобетона, бетона, керамзитобетона массой до 3 т 1 т груза 15,784 Транспортировка демонтированных материалов на базу ул.Каменская,4а 19 Погрузо-разгрузочные работы при автомобильных перевозках: Погрузка труб металлических с применением автомобильных кранов труб 1 т груза 0,22 20 Погрузка при автомобильных перевозках стальных профилей мелких (остальные виды стали, не указанные в расценке -027) - краны, фланцы 1 т груза 0,153 21 Погрузка при автомобильных перевозках прочих материалов, деталей (с использованием погрузчика) люки 1 т груза 0,064 22 Перевозка грузов I класса автомобилями бортовыми грузоподъемностью до 15 т на расстояние до 3 км 1 т груза 0,437 23 Погрузо-разгрузочные работы при автомобильных перевозках: Разгрузка труб металлических с применением автомобильных кранов 1 т груза 0,22 24 Разгрузка при автомобильных перевозках стальных профилей мелких (остальные виды стали, не указанные в расценке -027) 1 т груза 0,153 25 Разгрузка при автомобильных перевозках прочих материалов, деталей (с использованием погрузчика) 1 т груза 0,064 Строительные работы камера Т 74  лист 2,3 чер.277/2026-АС 26 Устройство основания под фундаменты: щебеночного м3 1,3 27 Устройство фундаментных плит бетонных плоских плита днища м3 1,9 28 Установка блоков стен подвалов массой: до 1,5 т - ФБС24-4</t>
+          <t>трубы (от Т 74 до Т 75) Вытесненный объем грунта который не будет завозиться: 67,79+(0,936+0,845+1,769+2, 3)= 73,64 м3 - песчаное основание+трубы и футляры Откопка камеры Т 74 =16,73 м3 Объём разбираемого асфальтобетонного покрытия= 19*1,15*0,13 = 2,84 м3 Объём щебеночного основания для восстановления дорог = 19*1,15*0,3 = 6,56 м3 Объём обратной засыпки 297-73,64-(2,84+6, 56)= 213,96 м3 1 Перевозка грузов I класса автомобилями-самосвалами грузоподъемностью 10 т работающих вне карьера на расстояние до 3 км 1 т груза 406,524 2 Засыпка траншей и котлованов с перемещением грунта до 5 м бульдозерами мощностью: 59 кВт (80 л.с .), группа грунтов 2 м3 214 3 Уплотнение грунта пневматическими трамбовками, группа грунтов: 1-2 м3 42,79 4 Устройство подстилающих и выравнивающих слоев оснований: из щебня м3 6,56 5 Планировка площадей бульдозерами мощностью: 59 кВт (80л.с.) м2 655 Разборка камеры Т74 6 Демонтаж чугунных люков шт 1 7 Демонтаж плит перекрытий камер площадью: до 5 м2 шт 2 8 Демонтаж блоков стен подвалов массой: до 0,5 т ( фбс 9.4.6) шт 9 9 Демонтаж блоков стен подвалов массой: до 1,5 т ( фбс 24.4.6) шт 9 10 Разборка кирпичной кладки камеры вручную : без очистки кирпича м3 0,5 Демонтаж трубопровода в камере Т74 11 Демонтаж стальных трубопроводов в ТК при номинальном давлении 1,6 МПа, температуре 150°С, диаметр труб: 65 мм + з/арматура км 0,003175 12 Демонтаж стальных трубопроводов в ТК при номинальном давлении 1,6 МПа, температуре 150°С, диаметр труб: 150 мм + з/арматура км 0,0109 ЧИСТКА КАМЕР согласно п.4 общих указаний чер.277/2026-ТС л.1.8 13 Очистка камер: от сухого ила и грязи без труб и арматуры м3 0,3 Транспортировка строительного мусора на полигон ТБО 14 Погрузо-разгрузочные работы при автомобильных перевозках: Погрузка мусора строительного с погрузкой экскаваторами емкостью ковша до 0,5 м 3 изоляция , кирпич 1 т груза 1,05 15 Перевозка грузов I класса автомобилями-самосвалами грузоподъемностью 10 т работающих вне карьера на расстояние до 8 км 1 т груза 1,05 16 Погрузка при автомобильных перевозках изделий из сборного железобетона, бетона, керамзитобетона массой до 3 т 1 т груза 15,784 17 Перевозка грузов I класса автомобилями-самосвалами грузоподъемностью 10 т работающих вне карьера на расстояние до 8 км 1 т груза 15,784 18 Разгрузка при автомобильных перевозках изделий из сборного железобетона, бетона, керамзитобетона массой до 3 т 1 т груза 15,784 Транспортировка демонтированных материалов на базу ул.Каменская,4а 19 Погрузо-разгрузочные работы при автомобильных перевозках: Погрузка труб металлических с применением автомобильных кранов труб 1 т груза 0,22 20 Погрузка при автомобильных перевозках стальных профилей мелких (остальные виды стали, не указанные в расценке -027) - краны, фланцы 1 т груза 0,153 21 Погрузка при автомобильных перевозках прочих материалов, деталей (с использованием погрузчика) люки 1 т груза 0,064 22 Перевозка грузов I класса автомобилями бортовыми грузоподъемностью до 15 т на расстояние до 3 км 1 т груза 0,437 23 Погрузо-разгрузочные работы при автомобильных перевозках: Разгрузка труб металлических с применением автомобильных кранов 1 т груза 0,22 24 Разгрузка при автомобильных перевозках стальных профилей мелких (остальные виды стали, не указанные в расценке -027) 1 т груза 0,153 25 Разгрузка при автомобильных перевозках прочих материалов, деталей (с использованием погрузчика) 1 т груза 0,064 Строительные работы камера Т 74 лист 2,3 чер.277/2026-АС 26 Устройство основания под фундаменты: щебеночного м3 1,3 27 Устройство фундаментных плит бетонных плоских плита днища м3 1,9 28 Установка блоков стен подвалов массой: до 1,5 т - ФБС24-4</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -541,10 +541,20 @@
         <v>0</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>НМЦК из обоснования:</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>1395620</v>
+      </c>
+    </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Источник: Договор подряда.docx</t>
+          <t>Источник: 852480203.txt</t>
         </is>
       </c>
     </row>

--- a/vse-loti/339406910/spec-339406910.xlsx
+++ b/vse-loti/339406910/spec-339406910.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00&quot; ₽&quot;"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -58,12 +61,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,14 +441,14 @@
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -505,7 +512,7 @@
           <t>трубы (от Т 74 до Т 75) Вытесненный объем грунта который не будет завозиться: 67,79+(0,936+0,845+1,769+2, 3)= 73,64 м3 - песчаное основание+трубы и футляры Откопка камеры Т 74 =16,73 м3 Объём разбираемого асфальтобетонного покрытия= 19*1,15*0,13 = 2,84 м3 Объём щебеночного основания для восстановления дорог = 19*1,15*0,3 = 6,56 м3 Объём обратной засыпки 297-73,64-(2,84+6, 56)= 213,96 м3 1 Перевозка грузов I класса автомобилями-самосвалами грузоподъемностью 10 т работающих вне карьера на расстояние до 3 км 1 т груза 406,524 2 Засыпка траншей и котлованов с перемещением грунта до 5 м бульдозерами мощностью: 59 кВт (80 л.с .), группа грунтов 2 м3 214 3 Уплотнение грунта пневматическими трамбовками, группа грунтов: 1-2 м3 42,79 4 Устройство подстилающих и выравнивающих слоев оснований: из щебня м3 6,56 5 Планировка площадей бульдозерами мощностью: 59 кВт (80л.с.) м2 655 Разборка камеры Т74 6 Демонтаж чугунных люков шт 1 7 Демонтаж плит перекрытий камер площадью: до 5 м2 шт 2 8 Демонтаж блоков стен подвалов массой: до 0,5 т ( фбс 9.4.6) шт 9 9 Демонтаж блоков стен подвалов массой: до 1,5 т ( фбс 24.4.6) шт 9 10 Разборка кирпичной кладки камеры вручную : без очистки кирпича м3 0,5 Демонтаж трубопровода в камере Т74 11 Демонтаж стальных трубопроводов в ТК при номинальном давлении 1,6 МПа, температуре 150°С, диаметр труб: 65 мм + з/арматура км 0,003175 12 Демонтаж стальных трубопроводов в ТК при номинальном давлении 1,6 МПа, температуре 150°С, диаметр труб: 150 мм + з/арматура км 0,0109 ЧИСТКА КАМЕР согласно п.4 общих указаний чер.277/2026-ТС л.1.8 13 Очистка камер: от сухого ила и грязи без труб и арматуры м3 0,3 Транспортировка строительного мусора на полигон ТБО 14 Погрузо-разгрузочные работы при автомобильных перевозках: Погрузка мусора строительного с погрузкой экскаваторами емкостью ковша до 0,5 м 3 изоляция , кирпич 1 т груза 1,05 15 Перевозка грузов I класса автомобилями-самосвалами грузоподъемностью 10 т работающих вне карьера на расстояние до 8 км 1 т груза 1,05 16 Погрузка при автомобильных перевозках изделий из сборного железобетона, бетона, керамзитобетона массой до 3 т 1 т груза 15,784 17 Перевозка грузов I класса автомобилями-самосвалами грузоподъемностью 10 т работающих вне карьера на расстояние до 8 км 1 т груза 15,784 18 Разгрузка при автомобильных перевозках изделий из сборного железобетона, бетона, керамзитобетона массой до 3 т 1 т груза 15,784 Транспортировка демонтированных материалов на базу ул.Каменская,4а 19 Погрузо-разгрузочные работы при автомобильных перевозках: Погрузка труб металлических с применением автомобильных кранов труб 1 т груза 0,22 20 Погрузка при автомобильных перевозках стальных профилей мелких (остальные виды стали, не указанные в расценке -027) - краны, фланцы 1 т груза 0,153 21 Погрузка при автомобильных перевозках прочих материалов, деталей (с использованием погрузчика) люки 1 т груза 0,064 22 Перевозка грузов I класса автомобилями бортовыми грузоподъемностью до 15 т на расстояние до 3 км 1 т груза 0,437 23 Погрузо-разгрузочные работы при автомобильных перевозках: Разгрузка труб металлических с применением автомобильных кранов 1 т груза 0,22 24 Разгрузка при автомобильных перевозках стальных профилей мелких (остальные виды стали, не указанные в расценке -027) 1 т груза 0,153 25 Разгрузка при автомобильных перевозках прочих материалов, деталей (с использованием погрузчика) 1 т груза 0,064 Строительные работы камера Т 74 лист 2,3 чер.277/2026-АС 26 Устройство основания под фундаменты: щебеночного м3 1,3 27 Устройство фундаментных плит бетонных плоских плита днища м3 1,9 28 Установка блоков стен подвалов массой: до 1,5 т - ФБС24-4</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="2" t="n">
         <v>6</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -513,41 +520,41 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="H3" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H4" s="6" t="n">
         <v>1395620</v>
       </c>
     </row>

--- a/vse-loti/339406910/spec-339406910.xlsx
+++ b/vse-loti/339406910/spec-339406910.xlsx
@@ -66,8 +66,8 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -447,8 +447,6 @@
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -479,25 +477,15 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Цена за ед. (без НДС)</t>
+          <t>Стоимость (без НДС)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Цена за ед. (с НДС)</t>
+          <t>Цена за т (без НДС)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Стоимость (без НДС)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Цена за т (без НДС)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Цена за т (с НДС)</t>
         </is>
@@ -520,20 +508,11 @@
           <t>т</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -544,9 +523,6 @@
       <c r="E3" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="H3" s="6" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -554,14 +530,14 @@
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="F4" s="6" t="n">
         <v>1395620</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Источник: 852480203.txt</t>
+          <t>Источник: Техническое задание.docx</t>
         </is>
       </c>
     </row>

--- a/vse-loti/339406910/spec-339406910.xlsx
+++ b/vse-loti/339406910/spec-339406910.xlsx
@@ -16,11 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00&quot; ₽&quot;"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,12 +30,22 @@
     <font>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <i val="1"/>
     </font>
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF808080"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -45,7 +54,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00305496"/>
+        <fgColor rgb="FF305496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7E6E6"/>
       </patternFill>
     </fill>
   </fills>
@@ -61,16 +75,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -436,17 +462,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -457,35 +484,40 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Наименование позиции (⌀ + s, если указано)</t>
+          <t>Наименование позиции</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>D×s, мм</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Кол-во (исх.)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Ед. изм.</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Масса, т (приведённая)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Стоимость (без НДС)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Цена за т (без НДС)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Цена за т (с НДС)</t>
         </is>
@@ -497,47 +529,321 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>трубы (от Т 74 до Т 75) Вытесненный объем грунта который не будет завозиться: 67,79+(0,936+0,845+1,769+2, 3)= 73,64 м3 - песчаное основание+трубы и футляры Откопка камеры Т 74 =16,73 м3 Объём разбираемого асфальтобетонного покрытия= 19*1,15*0,13 = 2,84 м3 Объём щебеночного основания для восстановления дорог = 19*1,15*0,3 = 6,56 м3 Объём обратной засыпки 297-73,64-(2,84+6, 56)= 213,96 м3 1 Перевозка грузов I класса автомобилями-самосвалами грузоподъемностью 10 т работающих вне карьера на расстояние до 3 км 1 т груза 406,524 2 Засыпка траншей и котлованов с перемещением грунта до 5 м бульдозерами мощностью: 59 кВт (80 л.с .), группа грунтов 2 м3 214 3 Уплотнение грунта пневматическими трамбовками, группа грунтов: 1-2 м3 42,79 4 Устройство подстилающих и выравнивающих слоев оснований: из щебня м3 6,56 5 Планировка площадей бульдозерами мощностью: 59 кВт (80л.с.) м2 655 Разборка камеры Т74 6 Демонтаж чугунных люков шт 1 7 Демонтаж плит перекрытий камер площадью: до 5 м2 шт 2 8 Демонтаж блоков стен подвалов массой: до 0,5 т ( фбс 9.4.6) шт 9 9 Демонтаж блоков стен подвалов массой: до 1,5 т ( фбс 24.4.6) шт 9 10 Разборка кирпичной кладки камеры вручную : без очистки кирпича м3 0,5 Демонтаж трубопровода в камере Т74 11 Демонтаж стальных трубопроводов в ТК при номинальном давлении 1,6 МПа, температуре 150°С, диаметр труб: 65 мм + з/арматура км 0,003175 12 Демонтаж стальных трубопроводов в ТК при номинальном давлении 1,6 МПа, температуре 150°С, диаметр труб: 150 мм + з/арматура км 0,0109 ЧИСТКА КАМЕР согласно п.4 общих указаний чер.277/2026-ТС л.1.8 13 Очистка камер: от сухого ила и грязи без труб и арматуры м3 0,3 Транспортировка строительного мусора на полигон ТБО 14 Погрузо-разгрузочные работы при автомобильных перевозках: Погрузка мусора строительного с погрузкой экскаваторами емкостью ковша до 0,5 м 3 изоляция , кирпич 1 т груза 1,05 15 Перевозка грузов I класса автомобилями-самосвалами грузоподъемностью 10 т работающих вне карьера на расстояние до 8 км 1 т груза 1,05 16 Погрузка при автомобильных перевозках изделий из сборного железобетона, бетона, керамзитобетона массой до 3 т 1 т груза 15,784 17 Перевозка грузов I класса автомобилями-самосвалами грузоподъемностью 10 т работающих вне карьера на расстояние до 8 км 1 т груза 15,784 18 Разгрузка при автомобильных перевозках изделий из сборного железобетона, бетона, керамзитобетона массой до 3 т 1 т груза 15,784 Транспортировка демонтированных материалов на базу ул.Каменская,4а 19 Погрузо-разгрузочные работы при автомобильных перевозках: Погрузка труб металлических с применением автомобильных кранов труб 1 т груза 0,22 20 Погрузка при автомобильных перевозках стальных профилей мелких (остальные виды стали, не указанные в расценке -027) - краны, фланцы 1 т груза 0,153 21 Погрузка при автомобильных перевозках прочих материалов, деталей (с использованием погрузчика) люки 1 т груза 0,064 22 Перевозка грузов I класса автомобилями бортовыми грузоподъемностью до 15 т на расстояние до 3 км 1 т груза 0,437 23 Погрузо-разгрузочные работы при автомобильных перевозках: Разгрузка труб металлических с применением автомобильных кранов 1 т груза 0,22 24 Разгрузка при автомобильных перевозках стальных профилей мелких (остальные виды стали, не указанные в расценке -027) 1 т груза 0,153 25 Разгрузка при автомобильных перевозках прочих материалов, деталей (с использованием погрузчика) 1 т груза 0,064 Строительные работы камера Т 74 лист 2,3 чер.277/2026-АС 26 Устройство основания под фундаменты: щебеночного м3 1,3 27 Устройство фундаментных плит бетонных плоских плита днища м3 1,9 28 Установка блоков стен подвалов массой: до 1,5 т - ФБС24-4</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
+          <t>СМР по модернизации тепловой сети (Т-74 → Т-75, 131 м): земляные работы, демонтаж труб, монтаж трубопроводов, строительство камер, благоустройство — не наш профиль (трубы — материал в составе работ)</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>усл. ед.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Труба стальная 57×5, ГОСТ 10704-91</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>57×5</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>1.768</v>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Труба стальная 76×5, ГОСТ 10704-91</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>76×5</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Труба стальная 133×6, ГОСТ 10704-91</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>133×6</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Труба стальная 159×6, ГОСТ 10704-91</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>159×6</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>т</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="n">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Труба стальная 159×7, ГОСТ 10704-91</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>159×7</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>ИТОГО</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>НМЦК из обоснования:</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>1395620</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Источник: Техническое задание.docx</t>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Труба PE-RT тип II 75/140 SDR9 (ППУ-изоляция)</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>75/140</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>133.13</v>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Труба 95 тип II 160/200 (ППУ-изоляция)</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>160/200</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>266.52</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Труба PE-RT тип II 160/250 SDR9 (ППУ-изоляция)</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>160/250</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Труба стальная футляр Ø300 мм (неразрезной кожух)</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>300×…</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>ИТОГО материалы (справочно, м):</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="7" t="n">
+        <v>469.448</v>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="6" t="n"/>
+      <c r="I12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>ВСЕГО по смете (ЛСР № 06-01-02, текущий уровень):</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>ФОТ + накл.расх. + сметная прибыль + дог.коэф 0,95 + НДС 22%</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="8" t="n">
+        <v>1395620.31</v>
+      </c>
+      <c r="H13" s="6" t="n"/>
+      <c r="I13" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>НМЦК (без НДС):</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="n">
+        <v>1143951.07</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>НМЦК (с НДС):</t>
+        </is>
+      </c>
+      <c r="G16" s="11" t="n">
+        <v>1395620.31</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>Источник 1 (НМЦК, ОКПД2, площадка, сроки): 852480203.htm/txt — Извещение 32616316737</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>Источник 2 (ТЗ, ведомость объёмов): 852480195.txt — Техническое задание</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>Источник 3 (смета, итоги, материалы): прил.2 смета.xlsx — ЛСР № 06-01-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>Источник 4 (проект договора, сроки, гарантия): 852480202.txt</t>
         </is>
       </c>
     </row>
